--- a/Data/Home/BedroomTwo.Window001.xlsx
+++ b/Data/Home/BedroomTwo.Window001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709252248</v>
+        <v>1711845247</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709285792</v>
+        <v>1711879366</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709289616</v>
+        <v>1711890349</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709292123</v>
+        <v>1711893506</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709246039</v>
+        <v>1711929996</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709270223</v>
+        <v>1711964514</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +695,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +714,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709274400</v>
+        <v>1712019056</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,6 +732,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709276498</v>
+        <v>1712060360</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +769,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +788,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709331859</v>
+        <v>1712103699</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -793,6 +806,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +825,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709361070</v>
+        <v>1712143540</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -829,6 +843,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +862,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709418472</v>
+        <v>1712159714</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +880,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +899,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709455987</v>
+        <v>1712162845</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -901,6 +917,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +936,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709504110</v>
+        <v>1712190057</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -937,6 +954,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,7 +973,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709531463</v>
+        <v>1712222675</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -973,6 +991,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +1010,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709551335</v>
+        <v>1712278057</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1009,6 +1028,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1047,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709553791</v>
+        <v>1712322039</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1045,6 +1065,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1063,7 +1084,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709590944</v>
+        <v>1712367600</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1081,6 +1102,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1099,7 +1121,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709626205</v>
+        <v>1712408222</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1117,6 +1139,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,7 +1158,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709768558</v>
+        <v>1712535488</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1153,6 +1176,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1171,7 +1195,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709797092</v>
+        <v>1712573445</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1189,6 +1213,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1207,7 +1232,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709852246</v>
+        <v>1712623968</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1225,6 +1250,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,7 +1269,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709884096</v>
+        <v>1712658979</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1261,6 +1287,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1279,7 +1306,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709938150</v>
+        <v>1712708127</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1297,6 +1324,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1315,7 +1343,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709966407</v>
+        <v>1712746232</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1333,6 +1361,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1351,7 +1380,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1710023905</v>
+        <v>1712750045</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1369,6 +1398,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1387,7 +1417,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1710055175</v>
+        <v>1712753151</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1405,6 +1435,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1423,7 +1454,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1710109182</v>
+        <v>1712793844</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1441,6 +1472,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1459,7 +1491,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1710152266</v>
+        <v>1712832347</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1477,6 +1509,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1495,7 +1528,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1710198514</v>
+        <v>1712880083</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1513,6 +1546,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1531,7 +1565,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1710227448</v>
+        <v>1712920519</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1549,6 +1583,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1567,7 +1602,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1710288859</v>
+        <v>1712928795</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1585,6 +1620,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1639,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1710326985</v>
+        <v>1712931618</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1621,6 +1657,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1639,7 +1676,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1710457721</v>
+        <v>1712976683</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1657,6 +1694,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1675,7 +1713,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1710488422</v>
+        <v>1713011423</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1693,6 +1731,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1711,7 +1750,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1710500626</v>
+        <v>1713060309</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1729,6 +1768,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1747,7 +1787,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1710503013</v>
+        <v>1713103459</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1765,6 +1805,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1783,7 +1824,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1710542026</v>
+        <v>1713140097</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1801,6 +1842,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1819,7 +1861,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1710578064</v>
+        <v>1713187611</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1837,6 +1879,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1855,7 +1898,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1710628516</v>
+        <v>1713193050</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1873,6 +1916,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1891,7 +1935,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1710662354</v>
+        <v>1713196202</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1909,6 +1953,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,7 +1972,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1710715520</v>
+        <v>1713226457</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1945,6 +1990,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1963,7 +2009,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1710741396</v>
+        <v>1713265951</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1981,6 +2027,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1999,7 +2046,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1710801183</v>
+        <v>1713314458</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2017,6 +2064,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2035,7 +2083,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1710831932</v>
+        <v>1713356201</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2053,6 +2101,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2071,7 +2120,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1710892571</v>
+        <v>1713398920</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2089,6 +2138,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2107,7 +2157,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1710925693</v>
+        <v>1713442213</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2125,6 +2175,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2143,7 +2194,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1711061379</v>
+        <v>1713487620</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2161,6 +2212,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2179,7 +2231,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1711092512</v>
+        <v>1713522716</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2197,6 +2249,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2215,7 +2268,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1711147614</v>
+        <v>1713743847</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2233,6 +2286,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2251,7 +2305,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1711175093</v>
+        <v>1713789552</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2269,6 +2323,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2287,7 +2342,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1711236672</v>
+        <v>1713832764</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2305,6 +2360,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2323,7 +2379,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1711274764</v>
+        <v>1713876807</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2341,6 +2397,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2359,7 +2416,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1711322975</v>
+        <v>1713878818</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2377,6 +2434,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2395,7 +2453,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1711362134</v>
+        <v>1713882002</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2413,6 +2471,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2431,7 +2490,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1711412981</v>
+        <v>1713917508</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2449,6 +2508,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2467,7 +2527,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1711456433</v>
+        <v>1713964260</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2485,6 +2545,229 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Window_Operation</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1714006198</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Window001.state: open</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Window_Operation</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1714048068</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Window001.state: close</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Window_Operation</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1714090446</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Window001.state: open</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Window_Operation</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1714129295</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Window001.state: close</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Window_Operation</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1714143763</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Window001.state: open</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Window_Operation</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BedroomTwo</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1714146753</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>BedroomTwo.Window001.state: close</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
